--- a/financial-model/النموذج-المالي-بيلاتس.xlsx
+++ b/financial-model/النموذج-المالي-بيلاتس.xlsx
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,41 +133,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,10 +549,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -543,7 +560,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>الافتراضات الأساسية (عدّل الخلايا الصفراء فقط)</t>
+          <t>الافتراضات الأساسية</t>
         </is>
       </c>
     </row>
@@ -585,7 +602,7 @@
           <t>عدد أجهزة Reformer</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -597,15 +614,15 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>سعة الجهاز (عميلة/حصة)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+          <t>سعة الجهاز</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>عميلة</t>
+          <t>عميلة/حصة</t>
         </is>
       </c>
     </row>
@@ -615,7 +632,7 @@
           <t>عدد الحصص اليومية</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>7</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -630,7 +647,7 @@
           <t>أيام التشغيل شهرياً</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>26</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -645,7 +662,7 @@
           <t>سعر الحصة المفردة</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>150</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -660,7 +677,7 @@
           <t>الإيجار السنوي</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>204000</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -672,161 +689,47 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>رواتب الموظفات (شهري)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>27000</v>
+          <t>الطاقة الشهرية القصوى</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>1092</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ريال/شهر</t>
+          <t>حصة-عميلة</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>التأمينات + نهاية الخدمة (شهري)</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>2200</v>
+          <t>الإيراد الشهري عند 100%</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>163800</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ريال/شهر</t>
+          <t>ريال</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>كهرباء وماء (شهري)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>3800</v>
+          <t>معدل الخصم لـ NPV</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0.15</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ريال/شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>نظام الحجز + اتصالات (شهري)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>ريال/شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>التسويق (شهري)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>ريال/شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>مستهلكات وغسيل (شهري)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ريال/شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>صيانة الأجهزة (شهري)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>ريال/شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>محاسبة وإداريات (شهري)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>ريال/شهر</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>معدل الخصم لحساب NPV</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
           <t>نسبة</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>الطاقة الشهرية القصوى (حصة-عميلة)</t>
-        </is>
-      </c>
-      <c r="B19" s="7">
-        <f>الافتراضات!$B$4*الافتراضات!$B$5*الافتراضات!$B$6*الافتراضات!$B$7</f>
-        <v/>
-      </c>
-      <c r="C19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>الإيراد الشهري عند 100% إشغال</t>
-        </is>
-      </c>
-      <c r="B20" s="7">
-        <f>الافتراضات!$B$19*الافتراضات!$B$8</f>
-        <v/>
-      </c>
-      <c r="C20" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -852,7 +755,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>التكلفة التأسيسية (CapEx) — بالريال السعودي</t>
+          <t>التكلفة التأسيسية (CapEx) — ريال</t>
         </is>
       </c>
     </row>
@@ -874,7 +777,7 @@
           <t>أجهزة Reformer مُورّدة (FOB+شحن+جمارك+نقل)</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="n">
         <v>41000</v>
       </c>
     </row>
@@ -884,7 +787,7 @@
           <t>أدوات مساعدة (Props)</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="9" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -894,7 +797,7 @@
           <t>ديكور وتجهيز داخلي وأثاث</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>80000</v>
       </c>
     </row>
@@ -904,7 +807,7 @@
           <t>لوحة خارجية وأنظمة تقنية وكاميرات</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -914,7 +817,7 @@
           <t>رخص وتراخيص حكومية</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -924,19 +827,18 @@
           <t>احتياطي طوارئ</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>إجمالي التأسيس (قبل رأس المال العامل)</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(B3:B8)</f>
-        <v/>
+      <c r="B9" s="7" t="n">
+        <v>175000</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +847,18 @@
           <t>رأس المال العامل</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>100000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>إجمالي الاستثمار المطلوب</t>
         </is>
       </c>
-      <c r="B11" s="10">
-        <f>B9+B10</f>
-        <v/>
+      <c r="B11" s="12" t="n">
+        <v>275000</v>
       </c>
     </row>
   </sheetData>
@@ -1006,9 +907,8 @@
           <t>الإيجار (سنوي ÷ 12)</t>
         </is>
       </c>
-      <c r="B3" s="8">
-        <f>الافتراضات!$B$9/12</f>
-        <v/>
+      <c r="B3" s="9" t="n">
+        <v>17000</v>
       </c>
     </row>
     <row r="4">
@@ -1017,9 +917,8 @@
           <t>رواتب الموظفات</t>
         </is>
       </c>
-      <c r="B4" s="8">
-        <f>الافتراضات!$B$10</f>
-        <v/>
+      <c r="B4" s="9" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="5">
@@ -1028,9 +927,8 @@
           <t>التأمينات + نهاية الخدمة</t>
         </is>
       </c>
-      <c r="B5" s="8">
-        <f>الافتراضات!$B$11</f>
-        <v/>
+      <c r="B5" s="9" t="n">
+        <v>2200</v>
       </c>
     </row>
     <row r="6">
@@ -1039,9 +937,8 @@
           <t>كهرباء وماء</t>
         </is>
       </c>
-      <c r="B6" s="8">
-        <f>الافتراضات!$B$12</f>
-        <v/>
+      <c r="B6" s="9" t="n">
+        <v>3800</v>
       </c>
     </row>
     <row r="7">
@@ -1050,9 +947,8 @@
           <t>نظام الحجز + اتصالات</t>
         </is>
       </c>
-      <c r="B7" s="8">
-        <f>الافتراضات!$B$13</f>
-        <v/>
+      <c r="B7" s="9" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
@@ -1061,9 +957,8 @@
           <t>التسويق</t>
         </is>
       </c>
-      <c r="B8" s="8">
-        <f>الافتراضات!$B$14</f>
-        <v/>
+      <c r="B8" s="9" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="9">
@@ -1072,9 +967,8 @@
           <t>مستهلكات وغسيل وتنظيف</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <f>الافتراضات!$B$15</f>
-        <v/>
+      <c r="B9" s="9" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
@@ -1083,9 +977,8 @@
           <t>صيانة الأجهزة</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>الافتراضات!$B$16</f>
-        <v/>
+      <c r="B10" s="9" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -1094,20 +987,18 @@
           <t>محاسبة وإداريات</t>
         </is>
       </c>
-      <c r="B11" s="8">
-        <f>الافتراضات!$B$17</f>
-        <v/>
+      <c r="B11" s="9" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>إجمالي المصروف التشغيلي الشهري</t>
         </is>
       </c>
-      <c r="B12" s="10">
-        <f>SUM(B3:B11)</f>
-        <v/>
+      <c r="B12" s="12" t="n">
+        <v>61000</v>
       </c>
     </row>
   </sheetData>
@@ -1127,17 +1018,17 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>سيناريوهات الإشغال (الأرقام تتحدّث تلقائياً من الافتراضات)</t>
+          <t>سيناريوهات الإشغال</t>
         </is>
       </c>
     </row>
@@ -1169,218 +1060,186 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>نسبة الإشغال</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="14" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>المقاعد المباعة/شهر</t>
         </is>
       </c>
-      <c r="B4" s="13">
-        <f>ROUND(B3*الافتراضات!$B$19,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="13">
-        <f>ROUND(C3*الافتراضات!$B$19,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="13">
-        <f>ROUND(D3*الافتراضات!$B$19,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>ROUND(E3*الافتراضات!$B$19,0)</f>
-        <v/>
+      <c r="B4" s="15" t="n">
+        <v>328</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>546</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>764</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>983</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>متوسط العميلات/حصة</t>
         </is>
       </c>
-      <c r="B5" s="13">
-        <f>ROUND(B3*الافتراضات!$B$4,1)</f>
-        <v/>
-      </c>
-      <c r="C5" s="13">
-        <f>ROUND(C3*الافتراضات!$B$4,1)</f>
-        <v/>
-      </c>
-      <c r="D5" s="13">
-        <f>ROUND(D3*الافتراضات!$B$4,1)</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>ROUND(E3*الافتراضات!$B$4,1)</f>
-        <v/>
+      <c r="B5" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>الإيراد الشهري (ريال)</t>
         </is>
       </c>
-      <c r="B6" s="13">
-        <f>B4*الافتراضات!$B$8</f>
-        <v/>
-      </c>
-      <c r="C6" s="13">
-        <f>C4*الافتراضات!$B$8</f>
-        <v/>
-      </c>
-      <c r="D6" s="13">
-        <f>D4*الافتراضات!$B$8</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>E4*الافتراضات!$B$8</f>
-        <v/>
+      <c r="B6" s="9" t="n">
+        <v>49140</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>81900</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>114660</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>147420</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>المصروف التشغيلي الشهري</t>
         </is>
       </c>
-      <c r="B7" s="13">
-        <f>-'التكاليف التشغيلية'!$B$12</f>
-        <v/>
-      </c>
-      <c r="C7" s="13">
-        <f>-'التكاليف التشغيلية'!$B$12</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>-'التكاليف التشغيلية'!$B$12</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>-'التكاليف التشغيلية'!$B$12</f>
-        <v/>
+      <c r="B7" s="9" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>-61000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>صافي الربح الشهري (ريال)</t>
-        </is>
-      </c>
-      <c r="B8" s="14">
-        <f>B6+B7</f>
-        <v/>
-      </c>
-      <c r="C8" s="14">
-        <f>C6+C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="14">
-        <f>D6+D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="14">
-        <f>E6+E7</f>
-        <v/>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>صافي الربح الشهري</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>-11860</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>20900</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>53660</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>86420</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>صافي الربح السنوي (ريال)</t>
-        </is>
-      </c>
-      <c r="B9" s="14">
-        <f>B8*12</f>
-        <v/>
-      </c>
-      <c r="C9" s="14">
-        <f>C8*12</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>D8*12</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>E8*12</f>
-        <v/>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>صافي الربح السنوي</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>-142320</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>250800</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>643920</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>1037040</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>فترة الاسترداد (شهر)</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>IF(B8&gt;0,ROUND('التكلفة التأسيسية'!$B$11/B8,1),"لا يُسترد")</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>IF(C8&gt;0,ROUND('التكلفة التأسيسية'!$B$11/C8,1),"لا يُسترد")</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>IF(D8&gt;0,ROUND('التكلفة التأسيسية'!$B$11/D8,1),"لا يُسترد")</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>IF(E8&gt;0,ROUND('التكلفة التأسيسية'!$B$11/E8,1),"لا يُسترد")</f>
-        <v/>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>لا يُسترد</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>13.1578947368421</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>5.124860231084607</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>3.182133765332099</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>ROI سنوي</t>
         </is>
       </c>
-      <c r="B11" s="12">
-        <f>B9/'التكلفة التأسيسية'!$B$11</f>
-        <v/>
-      </c>
-      <c r="C11" s="12">
-        <f>C9/'التكلفة التأسيسية'!$B$11</f>
-        <v/>
-      </c>
-      <c r="D11" s="12">
-        <f>D9/'التكلفة التأسيسية'!$B$11</f>
-        <v/>
-      </c>
-      <c r="E11" s="12">
-        <f>E9/'التكلفة التأسيسية'!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="B11" s="14" t="n">
+        <v>-0.5175272727272727</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>2.341527272727273</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>3.771054545454545</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>نقطة التعادل (نسبة إشغال)</t>
         </is>
       </c>
-      <c r="B13" s="16">
-        <f>'التكاليف التشغيلية'!$B$12/الافتراضات!$B$20</f>
-        <v/>
+      <c r="B13" s="20" t="n">
+        <v>0.3724053724053724</v>
       </c>
     </row>
   </sheetData>
@@ -1397,16 +1256,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1454,197 +1313,197 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>متوسط الإشغال</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="18" t="n">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
         <v>0.38</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="14" t="n">
         <v>0.55</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="14" t="n">
         <v>0.63</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="14" t="n">
         <v>0.68</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="14" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>الإيراد السنوي</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="13">
-        <f>C3*الافتراضات!$B$19*الافتراضات!$B$8*12</f>
-        <v/>
-      </c>
-      <c r="D4" s="13">
-        <f>D3*الافتراضات!$B$19*الافتراضات!$B$8*12</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>E3*الافتراضات!$B$19*الافتراضات!$B$8*12</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>F3*الافتراضات!$B$19*الافتراضات!$B$8*12</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>G3*الافتراضات!$B$19*الافتراضات!$B$8*12</f>
-        <v/>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>746928</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>1081080</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1238328</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>1336608</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>1375920</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>المصروف السنوي</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="5" t="n">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>762000</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="9" t="n">
         <v>754000</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="9" t="n">
         <v>885000</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="9" t="n">
         <v>911000</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="9" t="n">
         <v>938000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>صافي التدفق النقدي</t>
         </is>
       </c>
-      <c r="B6" s="19">
-        <f>-'التكلفة التأسيسية'!$B$11</f>
-        <v/>
-      </c>
-      <c r="C6" s="14">
-        <f>C4-C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="14">
-        <f>D4-D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
-        <f>E4-E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="14">
-        <f>F4-F5</f>
-        <v/>
-      </c>
-      <c r="G6" s="14">
-        <f>G4-G5</f>
-        <v/>
+      <c r="B6" s="21" t="n">
+        <v>-275000</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>-15072</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>327080</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>353328</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>425608.0000000002</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>437920</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>التدفق التراكمي</t>
         </is>
       </c>
-      <c r="B7" s="13">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="13">
-        <f>B7+C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>C7+D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>D7+E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>E7+F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>F7+G6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="9" t="n">
+        <v>-275000</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>-290072</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>37008</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>390336</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>815944.0000000002</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>1253864</v>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>المؤشرات المالية</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
+      <c r="B9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>NPV (صافي القيمة الحالية)</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>B6+NPV(الافتراضات!$B$18,C6:G6)</f>
-        <v/>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>NPV @ 15%</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>652598.6703878278</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>NPV @ 12%</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>742750.0689816742</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>IRR (معدل العائد الداخلي)</t>
         </is>
       </c>
-      <c r="B11" s="20">
-        <f>IRR(B6:G6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B12" s="22" t="n">
+        <v>0.6651648921368177</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>إجمالي صافي التدفقات (5 سنوات)</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(C6:G6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="n">
+        <v>1528864</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>نقطة التعادل (إشغال)</t>
         </is>
       </c>
-      <c r="B13" s="20">
-        <f>'التكاليف التشغيلية'!$B$12*12/(الافتراضات!$B$19*الافتراضات!$B$8*12)</f>
-        <v/>
+      <c r="B14" s="22" t="n">
+        <v>0.3724053724053724</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
